--- a/14-gather_case_list/脚本单元测试案例.xlsx
+++ b/14-gather_case_list/脚本单元测试案例.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="21216" windowHeight="9024"/>
   </bookViews>
   <sheets>
-    <sheet name="单文件读取测试" sheetId="1" r:id="rId1"/>
+    <sheet name="脚本测试案例" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">脚本测试案例!$A$1:$F$17</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>序号</t>
   </si>
@@ -56,7 +59,7 @@
     <t>系统能正常打开并解析源文件，无乱码或内存溢出</t>
   </si>
   <si>
-    <t>PASS</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>单个文件的写入和保存</t>
@@ -86,9 +89,6 @@
     <t>当某个子项检查结果为“不通过”时，目标文件应如实记录该状态</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
     <t>总检查结果更新（正向）</t>
   </si>
   <si>
@@ -137,7 +137,7 @@
     <t>缺失表写入反馈</t>
   </si>
   <si>
-    <t>检查目标表不存在时，将详细错误信息直接写入到最终目标报告中</t>
+    <t>检查目标表数据不存在时，将详细错误信息直接写入到最终目标报告中</t>
   </si>
   <si>
     <t>主键检核测试</t>
@@ -159,6 +159,27 @@
   </si>
   <si>
     <t>存在单条或多条主键违规时，条数统计需准确，且检核结果标为“N”，测试结果标为“不通过”</t>
+  </si>
+  <si>
+    <t>多表条数案例测试</t>
+  </si>
+  <si>
+    <t>不同表的案例统计</t>
+  </si>
+  <si>
+    <t>测试同一层表（同文件内）上述测试用例是否正确识别</t>
+  </si>
+  <si>
+    <t>非标层级测试</t>
+  </si>
+  <si>
+    <t>不在配置文件中案例处理</t>
+  </si>
+  <si>
+    <t>没有配置对应的案例文件或清单信息的，直接忽略文件执行，并在日志体现</t>
+  </si>
+  <si>
+    <t>PENDING</t>
   </si>
 </sst>
 </file>
@@ -171,7 +192,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +229,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -367,6 +401,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -433,12 +479,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -476,12 +516,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,58 +727,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -756,74 +784,80 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -840,21 +874,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1382,7 +1422,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="39.5555555555556" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="6.33333333333333" style="2" customWidth="1"/>
@@ -1396,283 +1436,345 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:6">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:6">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:6">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:6">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="E5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:6">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:6">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:6">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:6">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:6">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="D8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:6">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:6">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:6">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:6">
-      <c r="A10" s="7">
+      <c r="D10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:6">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="1:6">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:6">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="B13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:6">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:6">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:6">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:6">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" ht="42" customHeight="1" spans="1:6">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" ht="42" customHeight="1" spans="1:6">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" ht="42" customHeight="1" spans="1:6">
-      <c r="A15" s="7">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:6">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" ht="42" customHeight="1" spans="1:6">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" ht="42" customHeight="1" spans="1:6">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" ht="42" customHeight="1" spans="1:6">
-      <c r="A17" s="7">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="C18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
